--- a/data/trans_camb/P16A09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,51</t>
+          <t>-2,16; 2,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -0,27</t>
+          <t>-3,66; -0,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,04</t>
+          <t>-3,42; -0,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,34</t>
+          <t>-5,11; 0,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,13</t>
+          <t>-5,23; -0,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,77</t>
+          <t>-3,42; 1,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,85</t>
+          <t>-2,35; 1,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -0,63</t>
+          <t>-3,48; -0,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,31</t>
+          <t>-2,64; 0,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,12; 166,0</t>
+          <t>-64,69; 179,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 11,75</t>
+          <t>-100,0; 6,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,31; 22,75</t>
+          <t>-90,23; 5,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-89,58; 64,01</t>
+          <t>-92,21; 22,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,39; 30,9</t>
+          <t>-91,82; 12,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 113,5</t>
+          <t>-60,48; 86,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 49,39</t>
+          <t>-64,4; 69,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,04; -18,6</t>
+          <t>-88,24; -27,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 21,98</t>
+          <t>-65,24; 15,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,28</t>
+          <t>-1,14; 2,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -0,48</t>
+          <t>-2,69; -0,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,64</t>
+          <t>-1,38; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,46</t>
+          <t>-2,48; 2,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,77</t>
+          <t>-3,51; 0,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,83</t>
+          <t>-0,84; 3,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,65</t>
+          <t>-1,18; 1,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,14</t>
+          <t>-2,4; -0,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,11</t>
+          <t>-0,75; 2,08</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 512,54</t>
+          <t>-63,69; 623,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 324,51</t>
+          <t>-71,07; 497,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 208,38</t>
+          <t>-69,62; 269,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,44; 117,21</t>
+          <t>-90,92; 143,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 322,36</t>
+          <t>-26,73; 359,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,96; 165,57</t>
+          <t>-47,33; 155,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-92,8; 8,72</t>
+          <t>-91,67; 7,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 192,64</t>
+          <t>-30,05; 197,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,42</t>
+          <t>-2,32; 1,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,38</t>
+          <t>-3,56; -0,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,69</t>
+          <t>-3,46; 0,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,79</t>
+          <t>-8,23; 1,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 2,89</t>
+          <t>-8,87; 2,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 7,49</t>
+          <t>-4,07; 7,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,15</t>
+          <t>-3,08; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -0,19</t>
+          <t>-4,04; -0,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,35</t>
+          <t>-3,44; 1,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,08; 83,34</t>
+          <t>-64,35; 91,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,02; -5,97</t>
+          <t>-92,92; -10,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,32; 35,01</t>
+          <t>-86,22; 27,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,44; 63,01</t>
+          <t>-80,69; 62,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,45; 84,83</t>
+          <t>-86,32; 87,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,61; 209,56</t>
+          <t>-44,69; 217,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 47,02</t>
+          <t>-62,61; 35,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 4,02</t>
+          <t>-82,11; -9,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 43,32</t>
+          <t>-70,0; 45,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; -0,6</t>
+          <t>-3,53; -0,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,9</t>
+          <t>-3,7; -0,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; -0,39</t>
+          <t>-3,22; -0,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,76</t>
+          <t>-2,92; 0,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,42</t>
+          <t>-3,99; -0,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,22</t>
+          <t>-3,69; 0,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,42</t>
+          <t>-2,85; -0,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -1,17</t>
+          <t>-3,36; -1,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; -0,45</t>
+          <t>-2,96; -0,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,79; -15,86</t>
+          <t>-66,66; -15,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,98; -24,08</t>
+          <t>-71,77; -22,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,19; -8,98</t>
+          <t>-61,03; -5,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,49; 27,97</t>
+          <t>-57,85; 28,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,66; -9,61</t>
+          <t>-76,99; -11,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 5,32</t>
+          <t>-71,89; 8,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,02; -10,02</t>
+          <t>-57,56; -14,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,29; -30,38</t>
+          <t>-69,55; -30,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,07; -16,18</t>
+          <t>-60,94; -15,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,52</t>
+          <t>-2,64; 1,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,28</t>
+          <t>-2,7; 1,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,28</t>
+          <t>-2,53; 1,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,39</t>
+          <t>-0,82; 4,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,16</t>
+          <t>-1,93; 3,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,52</t>
+          <t>-1,05; 4,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,58</t>
+          <t>-1,08; 2,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,48</t>
+          <t>-1,75; 1,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,8</t>
+          <t>-0,77; 2,82</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,07; 103,1</t>
+          <t>-66,1; 103,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,67; 84,02</t>
+          <t>-65,3; 87,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 89,49</t>
+          <t>-60,79; 102,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 121,23</t>
+          <t>-11,76; 110,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 86,4</t>
+          <t>-29,97; 89,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 109,83</t>
+          <t>-16,03; 125,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 76,85</t>
+          <t>-21,34; 80,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 45,36</t>
+          <t>-33,61; 48,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 82,35</t>
+          <t>-15,77; 82,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,0</t>
+          <t>-1,33; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-1,81; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,0</t>
+          <t>-1,48; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,34</t>
+          <t>0,66; 5,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,97</t>
+          <t>-3,11; 0,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,68</t>
+          <t>-1,27; 2,74</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,5</t>
+          <t>0,69; 4,58</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,52</t>
+          <t>-2,77; 0,41</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,71</t>
+          <t>-1,48; 1,63</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8,38; 91,38</t>
+          <t>7,96; 93,27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 17,23</t>
+          <t>-40,66; 17,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 47,84</t>
+          <t>-16,74; 50,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,35; 95,41</t>
+          <t>9,97; 99,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 11,45</t>
+          <t>-43,82; 10,54</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 37,17</t>
+          <t>-23,54; 34,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; -0,1</t>
+          <t>-1,66; -0,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,9</t>
+          <t>-2,38; -0,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; -0,46</t>
+          <t>-2,06; -0,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,92</t>
+          <t>-0,45; 1,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,51; -0,28</t>
+          <t>-2,43; -0,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,1</t>
+          <t>-1,24; 0,99</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,72</t>
+          <t>-0,7; 0,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,07; -0,78</t>
+          <t>-2,1; -0,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,12</t>
+          <t>-1,28; 0,1</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,11; -2,73</t>
+          <t>-49,05; -1,4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-68,85; -34,62</t>
+          <t>-68,63; -36,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,48; -17,83</t>
+          <t>-59,78; -19,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 42,85</t>
+          <t>-8,28; 39,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,75; -5,97</t>
+          <t>-41,9; -6,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 23,54</t>
+          <t>-22,19; 20,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 19,54</t>
+          <t>-15,97; 18,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-47,49; -21,73</t>
+          <t>-47,09; -22,21</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 3,29</t>
+          <t>-29,78; 2,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Clase-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-0,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,58</t>
+          <t>-2,0; 2,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -0,26</t>
+          <t>-3,7; -0,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -0,07</t>
+          <t>-3,51; -0,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 0,26</t>
+          <t>-5,06; 0,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,07</t>
+          <t>-5,38; -0,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,58</t>
+          <t>-3,72; 1,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,26</t>
+          <t>-2,28; 0,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -0,68</t>
+          <t>-3,47; -0,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,24</t>
+          <t>-2,61; 0,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-62,98%</t>
+          <t>-62,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-18,02%</t>
+          <t>-15,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-35,81%</t>
+          <t>-34,16%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,69; 179,45</t>
+          <t>-61,88; 205,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,64</t>
+          <t>-100,0; 16,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,23; 5,4</t>
+          <t>-89,25; 16,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-92,21; 22,2</t>
+          <t>-90,9; 37,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,82; 12,17</t>
+          <t>-92,42; 23,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,48; 86,18</t>
+          <t>-63,98; 78,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 69,63</t>
+          <t>-65,61; 53,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,24; -27,09</t>
+          <t>-88,74; -22,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 15,13</t>
+          <t>-63,9; 19,77</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,27</t>
+          <t>-0,97; 2,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,46</t>
+          <t>-2,67; -0,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,58</t>
+          <t>-1,29; 1,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,65</t>
+          <t>-2,53; 2,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,8</t>
+          <t>-3,62; 0,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,93</t>
+          <t>-0,6; 4,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,66</t>
+          <t>-1,22; 1,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,11</t>
+          <t>-2,47; -0,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,08</t>
+          <t>-0,61; 2,06</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,69; 623,69</t>
+          <t>-66,82; 530,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,07; 497,47</t>
+          <t>-71,19; 362,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 269,25</t>
+          <t>-68,39; 250,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,92; 143,44</t>
+          <t>-90,52; 91,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 359,6</t>
+          <t>-24,11; 386,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 155,29</t>
+          <t>-49,2; 144,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,67; 7,58</t>
+          <t>-92,08; 12,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 197,01</t>
+          <t>-29,45; 188,79</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>0,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,57</t>
+          <t>-2,44; 1,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,44</t>
+          <t>-3,71; -0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,53</t>
+          <t>-2,44; 1,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 1,85</t>
+          <t>-7,88; 1,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 2,37</t>
+          <t>-8,21; 1,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 7,8</t>
+          <t>-4,06; 7,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,9</t>
+          <t>-2,84; 0,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,49</t>
+          <t>-3,99; -0,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,43</t>
+          <t>-1,79; 2,78</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-44,11%</t>
+          <t>-15,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-21,94%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,35; 91,34</t>
+          <t>-65,95; 80,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,92; -10,28</t>
+          <t>-92,35; -12,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,22; 27,08</t>
+          <t>-65,5; 83,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,69; 62,32</t>
+          <t>-78,54; 63,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,32; 87,35</t>
+          <t>-86,35; 69,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 217,88</t>
+          <t>-44,38; 213,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-62,61; 35,36</t>
+          <t>-61,26; 34,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,11; -9,46</t>
+          <t>-82,78; -6,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 45,56</t>
+          <t>-39,08; 100,81</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-1,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,62</t>
+          <t>-3,56; -0,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,93</t>
+          <t>-3,64; -0,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,28</t>
+          <t>-3,22; -0,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,79</t>
+          <t>-2,88; 0,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -0,55</t>
+          <t>-3,87; -0,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,33</t>
+          <t>-2,42; 1,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,53</t>
+          <t>-2,8; -0,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -1,2</t>
+          <t>-3,31; -1,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,45</t>
+          <t>-2,4; -0,14</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-40,02%</t>
+          <t>-40,56%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-35,92%</t>
+          <t>-14,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-38,76%</t>
+          <t>-30,09%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,66; -15,37</t>
+          <t>-67,38; -11,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,77; -22,15</t>
+          <t>-70,42; -19,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,03; -5,23</t>
+          <t>-62,26; -4,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 28,7</t>
+          <t>-57,97; 30,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,99; -11,64</t>
+          <t>-75,64; -10,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,89; 8,2</t>
+          <t>-46,05; 42,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,56; -14,49</t>
+          <t>-57,25; -12,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,55; -30,68</t>
+          <t>-70,28; -31,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,94; -15,4</t>
+          <t>-48,68; -4,32</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>0,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,53</t>
+          <t>-2,96; 1,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,37</t>
+          <t>-2,95; 1,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,4</t>
+          <t>-2,96; 1,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,2</t>
+          <t>-0,8; 4,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,34</t>
+          <t>-1,93; 3,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,97</t>
+          <t>-0,66; 4,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,5</t>
+          <t>-1,24; 2,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,52</t>
+          <t>-1,75; 1,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,82</t>
+          <t>-0,83; 2,46</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-17,57%</t>
+          <t>-23,35%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,1; 103,47</t>
+          <t>-67,4; 91,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 87,2</t>
+          <t>-65,19; 75,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 102,09</t>
+          <t>-68,42; 82,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 110,51</t>
+          <t>-12,68; 119,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 89,71</t>
+          <t>-30,56; 85,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 125,88</t>
+          <t>-10,55; 119,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 80,12</t>
+          <t>-22,91; 75,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 48,41</t>
+          <t>-33,29; 46,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 82,41</t>
+          <t>-15,71; 75,43</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,0</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,0</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,0</t>
+          <t>-1,5; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,43</t>
+          <t>0,58; 5,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,96</t>
+          <t>-3,11; 0,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,74</t>
+          <t>-1,22; 2,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,58</t>
+          <t>0,32; 4,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,41</t>
+          <t>-2,87; 0,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,63</t>
+          <t>-1,25; 2,05</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,96; 93,27</t>
+          <t>6,19; 97,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 17,06</t>
+          <t>-40,82; 17,03</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 50,04</t>
+          <t>-15,82; 52,16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,97; 99,01</t>
+          <t>3,81; 89,02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 10,54</t>
+          <t>-44,96; 12,37</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 34,36</t>
+          <t>-19,57; 45,34</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; -0,06</t>
+          <t>-1,67; -0,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,92</t>
+          <t>-2,42; -0,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,47</t>
+          <t>-1,77; -0,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,82</t>
+          <t>-0,36; 1,92</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; -0,29</t>
+          <t>-2,23; -0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,99</t>
+          <t>-0,61; 1,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,67</t>
+          <t>-0,72; 0,63</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,84</t>
+          <t>-2,11; -0,8</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,1</t>
+          <t>-0,94; 0,28</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-40,2%</t>
+          <t>-36,37%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-13,63%</t>
+          <t>-7,4%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,05; -1,4</t>
+          <t>-50,53; -0,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-68,63; -36,22</t>
+          <t>-69,05; -35,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,78; -19,62</t>
+          <t>-52,56; -11,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 39,73</t>
+          <t>-6,68; 42,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-41,9; -6,0</t>
+          <t>-41,2; -6,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 20,99</t>
+          <t>-10,5; 31,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 18,96</t>
+          <t>-16,92; 17,44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-47,09; -22,21</t>
+          <t>-48,02; -21,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 2,43</t>
+          <t>-21,35; 7,84</t>
         </is>
       </c>
     </row>
